--- a/databases/tabela_contingencia_final.xlsx
+++ b/databases/tabela_contingencia_final.xlsx
@@ -382,14 +382,20 @@
           <t>Highest rates</t>
         </is>
       </c>
-      <c r="B2">
-        <v>522</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>67</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>22 (0.4%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>85 (1.5%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>561 (10.1%)</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -398,14 +404,20 @@
           <t>Intermediary rates</t>
         </is>
       </c>
-      <c r="B3">
-        <v>1524</v>
-      </c>
-      <c r="C3">
-        <v>115</v>
-      </c>
-      <c r="D3">
-        <v>481</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>146 (2.6%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>545 (9.8%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1616 (29%)</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -414,14 +426,20 @@
           <t>Lowest rates</t>
         </is>
       </c>
-      <c r="B4">
-        <v>1909</v>
-      </c>
-      <c r="C4">
-        <v>195</v>
-      </c>
-      <c r="D4">
-        <v>737</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>207 (3.7%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>682 (12.2%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1705 (30.6%)</t>
+        </is>
       </c>
     </row>
   </sheetData>
